--- a/templates/FIRFEMBVCP - template.xlsx
+++ b/templates/FIRFEMBVCP - template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20370" yWindow="-60" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$43</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="13.42578125" customWidth="1" style="55" min="1" max="1"/>
@@ -1238,8 +1238,8 @@
     <col width="5.42578125" customWidth="1" style="55" min="7" max="7"/>
     <col width="23.140625" bestFit="1" customWidth="1" style="55" min="8" max="8"/>
     <col width="23.42578125" bestFit="1" customWidth="1" style="55" min="9" max="9"/>
-    <col width="9.140625" customWidth="1" style="55" min="10" max="16"/>
-    <col width="9.140625" customWidth="1" style="55" min="17" max="16384"/>
+    <col width="9.140625" customWidth="1" style="55" min="10" max="17"/>
+    <col width="9.140625" customWidth="1" style="55" min="18" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" hidden="1">
@@ -1382,96 +1382,96 @@
     <row r="17" ht="15.95" customFormat="1" customHeight="1" s="33">
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C17" s="35" t="n">
-        <v>411.4177364</v>
+        <v>414.9914465</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>0.0003654125764191996</v>
+        <v>0.001103453684776934</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>0.0005298141560958758</v>
+        <v>0.0004681774334609479</v>
       </c>
       <c r="F17" s="37" t="n">
-        <v>0.6896995337230553</v>
+        <v>2.356913439034811</v>
       </c>
     </row>
     <row r="18" ht="15.95" customFormat="1" customHeight="1" s="33">
       <c r="B18" s="38" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C18" s="39" t="n">
-        <v>411.2674541</v>
+        <v>414.5340274</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>0.000495372708475994</v>
+        <v>0.0005561882684366193</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>0.0005298141560958758</v>
+        <v>0.0004681774334609479</v>
       </c>
       <c r="F18" s="41" t="n">
-        <v>0.9349933420547389</v>
+        <v>1.187986068284115</v>
       </c>
     </row>
     <row r="19" ht="15.95" customFormat="1" customHeight="1" s="33">
       <c r="B19" s="38" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C19" s="39" t="n">
-        <v>411.0638243</v>
+        <v>414.3035966</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>0.0003982156763013833</v>
+        <v>0.0005562856282006479</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>0.0005298141560958758</v>
+        <v>0.0004681774334609479</v>
       </c>
       <c r="F19" s="41" t="n">
-        <v>0.7516138852079327</v>
+        <v>1.188194023125742</v>
       </c>
     </row>
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="33">
       <c r="B20" s="38" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C20" s="39" t="n">
-        <v>410.9001974</v>
+        <v>414.0732536</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>0.0003982008990555119</v>
+        <v>0.0005546523775132872</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>0.0005298141560958758</v>
+        <v>0.0004681774334609479</v>
       </c>
       <c r="F20" s="41" t="n">
-        <v>0.7515859938318693</v>
+        <v>1.184705493840408</v>
       </c>
     </row>
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="33">
       <c r="B21" s="38" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C21" s="39" t="n">
-        <v>410.7366417</v>
+        <v>413.8437142</v>
       </c>
       <c r="D21" s="40" t="n">
-        <v>0.0003981848226899398</v>
+        <v>0.001694461929753199</v>
       </c>
       <c r="E21" s="40" t="n">
-        <v>0.0005298141560958758</v>
+        <v>0.0004681774334609479</v>
       </c>
       <c r="F21" s="41" t="n">
-        <v>0.751555650426758</v>
+        <v>3.61927296928236</v>
       </c>
     </row>
     <row r="22" ht="15.95" customHeight="1">
@@ -1511,18 +1511,18 @@
     <row r="24" ht="15.95" customFormat="1" customHeight="1" s="33">
       <c r="B24" s="42" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C24" s="42" t="inlineStr"/>
       <c r="D24" s="36" t="n">
-        <v>0.008714878660352365</v>
+        <v>0.005571479739490792</v>
       </c>
       <c r="E24" s="36" t="n">
-        <v>0.0101146136016641</v>
+        <v>0.00328184861989711</v>
       </c>
       <c r="F24" s="37" t="n">
-        <v>0.8616126135474472</v>
+        <v>1.697665061609534</v>
       </c>
       <c r="G24" s="43" t="n"/>
     </row>
@@ -1535,13 +1535,13 @@
       </c>
       <c r="C25" s="45" t="inlineStr"/>
       <c r="D25" s="40" t="n">
-        <v>0.009391362220317001</v>
+        <v>0.01344470315998691</v>
       </c>
       <c r="E25" s="40" t="n">
-        <v>0.01132875917954701</v>
+        <v>0.01295941951657564</v>
       </c>
       <c r="F25" s="41" t="n">
-        <v>0.8289841871890266</v>
+        <v>1.037446402810757</v>
       </c>
       <c r="G25" s="46" t="n"/>
       <c r="H25" s="47" t="n"/>
@@ -1555,13 +1555,13 @@
       </c>
       <c r="C26" s="45" t="inlineStr"/>
       <c r="D26" s="40" t="n">
-        <v>0.02491246145780646</v>
+        <v>0.03041965581409922</v>
       </c>
       <c r="E26" s="40" t="n">
-        <v>0.03245009308684765</v>
+        <v>0.0366340172059012</v>
       </c>
       <c r="F26" s="41" t="n">
-        <v>0.7677161785370571</v>
+        <v>0.8303663680432803</v>
       </c>
       <c r="G26" s="46" t="n"/>
     </row>
@@ -1574,13 +1574,13 @@
       </c>
       <c r="C27" s="45" t="inlineStr"/>
       <c r="D27" s="40" t="n">
-        <v>0.04578249625411335</v>
+        <v>0.05038151538962432</v>
       </c>
       <c r="E27" s="40" t="n">
-        <v>0.05658335107566748</v>
+        <v>0.06128941713981373</v>
       </c>
       <c r="F27" s="41" t="n">
-        <v>0.8091160276613801</v>
+        <v>0.8220263422426379</v>
       </c>
       <c r="G27" s="46" t="n"/>
     </row>
@@ -1593,13 +1593,13 @@
       </c>
       <c r="C28" s="45" t="inlineStr"/>
       <c r="D28" s="40" t="n">
-        <v>0.09080957510807619</v>
+        <v>0.0954608450049772</v>
       </c>
       <c r="E28" s="40" t="n">
-        <v>0.1101337668794071</v>
+        <v>0.1138976513825909</v>
       </c>
       <c r="F28" s="41" t="n">
-        <v>0.8245389010212436</v>
+        <v>0.8381283006821356</v>
       </c>
       <c r="G28" s="46" t="n"/>
     </row>
@@ -1607,18 +1607,18 @@
       <c r="A29" s="48" t="n"/>
       <c r="B29" s="45" t="inlineStr">
         <is>
-          <t>Ano 2026</t>
+          <t>Últimos 720 dias</t>
         </is>
       </c>
       <c r="C29" s="45" t="inlineStr"/>
       <c r="D29" s="40" t="n">
-        <v>0.02336017437456839</v>
+        <v>0.225507099782855</v>
       </c>
       <c r="E29" s="40" t="n">
-        <v>0.03025657239333213</v>
+        <v>0.2565285150959318</v>
       </c>
       <c r="F29" s="41" t="n">
-        <v>0.7720694225006283</v>
+        <v>0.8790722532289403</v>
       </c>
       <c r="G29" s="46" t="n"/>
     </row>
@@ -1626,18 +1626,18 @@
       <c r="A30" s="48" t="n"/>
       <c r="B30" s="45" t="inlineStr">
         <is>
-          <t>Ano 2025</t>
+          <t>Ano 2026</t>
         </is>
       </c>
       <c r="C30" s="45" t="inlineStr"/>
       <c r="D30" s="40" t="n">
-        <v>0.0999288549685704</v>
+        <v>0.03224941824407535</v>
       </c>
       <c r="E30" s="40" t="n">
-        <v>0.1146833322510794</v>
+        <v>0.03884110435965238</v>
       </c>
       <c r="F30" s="41" t="n">
-        <v>0.8713459315063621</v>
+        <v>0.8302909707576598</v>
       </c>
       <c r="G30" s="46" t="n"/>
     </row>
@@ -1645,18 +1645,18 @@
       <c r="A31" s="48" t="n"/>
       <c r="B31" s="45" t="inlineStr">
         <is>
-          <t>Ano 2024</t>
+          <t>Ano 2025</t>
         </is>
       </c>
       <c r="C31" s="45" t="inlineStr"/>
       <c r="D31" s="40" t="n">
-        <v>0.1142955896615951</v>
+        <v>0.0999288549685704</v>
       </c>
       <c r="E31" s="40" t="n">
-        <v>0.121916315493698</v>
+        <v>0.1146833322510794</v>
       </c>
       <c r="F31" s="41" t="n">
-        <v>0.9374921576226871</v>
+        <v>0.8713459315063621</v>
       </c>
       <c r="G31" s="46" t="n"/>
     </row>
@@ -1664,166 +1664,185 @@
       <c r="A32" s="48" t="n"/>
       <c r="B32" s="45" t="inlineStr">
         <is>
-          <t>Acumulado²</t>
+          <t>Ano 2024</t>
         </is>
       </c>
       <c r="C32" s="45" t="inlineStr"/>
       <c r="D32" s="40" t="n">
-        <v>3.114177364000001</v>
+        <v>0.1142955896615951</v>
       </c>
       <c r="E32" s="40" t="n">
-        <v>3.065246178501758</v>
+        <v>0.121916315493698</v>
       </c>
       <c r="F32" s="41" t="n">
-        <v>1.015963215562073</v>
+        <v>0.9374921576226871</v>
       </c>
       <c r="G32" s="46" t="n"/>
     </row>
-    <row r="33" ht="15.95" customHeight="1">
-      <c r="A33" s="12" t="n"/>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="26.1" customHeight="1">
+    <row r="33" ht="15.95" customFormat="1" customHeight="1" s="33">
+      <c r="A33" s="48" t="n"/>
+      <c r="B33" s="45" t="inlineStr">
+        <is>
+          <t>Acumulado²</t>
+        </is>
+      </c>
+      <c r="C33" s="45" t="inlineStr"/>
+      <c r="D33" s="40" t="n">
+        <v>3.149914465</v>
+      </c>
+      <c r="E33" s="40" t="n">
+        <v>3.099119522972872</v>
+      </c>
+      <c r="F33" s="41" t="n">
+        <v>1.01639012037148</v>
+      </c>
+      <c r="G33" s="46" t="n"/>
+    </row>
+    <row r="34" ht="15.95" customHeight="1">
       <c r="A34" s="12" t="n"/>
-      <c r="B34" s="54" t="inlineStr">
+      <c r="B34" s="13" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="4" t="n"/>
+    </row>
+    <row r="35" ht="26.1" customHeight="1">
+      <c r="A35" s="12" t="n"/>
+      <c r="B35" s="54" t="inlineStr">
         <is>
           <t>Patrimônio Líquido (R$)</t>
         </is>
       </c>
-      <c r="G34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="15.95" customHeight="1">
-      <c r="A35" s="16" t="n"/>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>Hoje¹</t>
-        </is>
-      </c>
-      <c r="C35" s="15" t="n"/>
-      <c r="D35" s="15" t="n"/>
-      <c r="E35" s="49" t="n">
-        <v>51417451.58</v>
-      </c>
-      <c r="F35" s="30" t="n"/>
       <c r="G35" s="4" t="n"/>
     </row>
     <row r="36" ht="15.95" customHeight="1">
       <c r="A36" s="16" t="n"/>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>Últimos 12 Meses (Média Diária)¹</t>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>Hoje¹</t>
         </is>
       </c>
       <c r="C36" s="15" t="n"/>
       <c r="D36" s="15" t="n"/>
       <c r="E36" s="49" t="n">
-        <v>69812477.61511905</v>
+        <v>51864080.51</v>
       </c>
       <c r="F36" s="30" t="n"/>
       <c r="G36" s="4" t="n"/>
     </row>
     <row r="37" ht="15.95" customHeight="1">
       <c r="A37" s="16" t="n"/>
-      <c r="B37" s="18" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>Últimos 12 Meses (Média Diária)¹</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="n"/>
+      <c r="D37" s="15" t="n"/>
+      <c r="E37" s="49" t="n">
+        <v>68358541.93011905</v>
+      </c>
+      <c r="F37" s="30" t="n"/>
       <c r="G37" s="4" t="n"/>
     </row>
     <row r="38" ht="15.95" customHeight="1">
-      <c r="A38" s="22" t="n"/>
-      <c r="B38" s="19" t="inlineStr">
+      <c r="A38" s="16" t="n"/>
+      <c r="B38" s="18" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+    </row>
+    <row r="39" ht="15.95" customHeight="1">
+      <c r="A39" s="22" t="n"/>
+      <c r="B39" s="19" t="inlineStr">
         <is>
           <t>¹Data de Referência:</t>
         </is>
       </c>
-      <c r="C38" s="20" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="D38" s="21" t="n"/>
-      <c r="E38" s="21" t="n"/>
-      <c r="F38" s="21" t="n"/>
-      <c r="G38" s="4" t="n"/>
-    </row>
-    <row r="39" ht="15.95" customHeight="1">
-      <c r="B39" s="20" t="inlineStr">
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="n"/>
+      <c r="E39" s="21" t="n"/>
+      <c r="F39" s="21" t="n"/>
+      <c r="G39" s="4" t="n"/>
+    </row>
+    <row r="40" ht="15.95" customHeight="1">
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">²Cota Inicial em: </t>
         </is>
       </c>
-      <c r="C39" s="20" t="inlineStr">
+      <c r="C40" s="20" t="inlineStr">
         <is>
           <t>2014-09-23</t>
         </is>
       </c>
-      <c r="D39" s="23" t="n"/>
-      <c r="E39" s="23" t="n"/>
-      <c r="F39" s="23" t="n"/>
-      <c r="G39" s="4" t="n"/>
-    </row>
-    <row r="40" ht="15.95" customHeight="1">
-      <c r="B40" s="24" t="n"/>
-      <c r="C40" s="25" t="n"/>
       <c r="D40" s="23" t="n"/>
       <c r="E40" s="23" t="n"/>
       <c r="F40" s="23" t="n"/>
       <c r="G40" s="4" t="n"/>
     </row>
-    <row r="41" ht="54" customHeight="1">
-      <c r="A41" s="4" t="n"/>
-      <c r="B41" s="56" t="inlineStr">
+    <row r="41" ht="15.95" customHeight="1">
+      <c r="B41" s="24" t="n"/>
+      <c r="C41" s="25" t="n"/>
+      <c r="D41" s="23" t="n"/>
+      <c r="E41" s="23" t="n"/>
+      <c r="F41" s="23" t="n"/>
+      <c r="G41" s="4" t="n"/>
+    </row>
+    <row r="42" ht="54" customHeight="1">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="56" t="inlineStr">
         <is>
           <t>As informações contidas neste material são de caráter exclusivamente informativo. Fundos de investimento não contam com garantia do administrador do fundo, do gestor da carteira, de qualquer mecanismo de seguro ou, ainda, do Fundo Garantidor de Créditos – FGC. Rentabilidade passada não representa garantia de rentabilidade futura. "A rentabilidade divulgada não é líquida de impostos.“ Leia o prospecto e o regulamento antes de investir.</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="n"/>
-      <c r="B42" s="57" t="n"/>
       <c r="G42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n"/>
-      <c r="B43" s="26" t="n"/>
-      <c r="C43" s="26" t="n"/>
-      <c r="D43" s="26" t="n"/>
-      <c r="E43" s="26" t="n"/>
-      <c r="F43" s="26" t="n"/>
+      <c r="B43" s="57" t="n"/>
       <c r="G43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n"/>
-      <c r="B44" s="27" t="n"/>
-      <c r="C44" s="28" t="n"/>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="11" t="n"/>
+      <c r="B44" s="26" t="n"/>
+      <c r="C44" s="26" t="n"/>
+      <c r="D44" s="26" t="n"/>
+      <c r="E44" s="26" t="n"/>
+      <c r="F44" s="26" t="n"/>
       <c r="G44" s="4" t="n"/>
     </row>
     <row r="45">
+      <c r="A45" s="4" t="n"/>
       <c r="B45" s="27" t="n"/>
       <c r="C45" s="28" t="n"/>
       <c r="D45" s="11" t="n"/>
       <c r="E45" s="11" t="n"/>
       <c r="F45" s="11" t="n"/>
+      <c r="G45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="27" t="n"/>
+      <c r="C46" s="28" t="n"/>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="11" t="n"/>
+      <c r="F46" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B35:F35"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="86" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="83"/>
 </worksheet>
 </file>